--- a/research/traditional_assets/database/data/germany/germany_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00413</v>
+        <v>-0.00624</v>
       </c>
       <c r="E2">
-        <v>0.1765</v>
+        <v>0.251</v>
       </c>
       <c r="F2">
-        <v>0.38</v>
+        <v>0.3345</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,88 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-6.161288995662619e-05</v>
+        <v>-2.463843130266467e-05</v>
       </c>
       <c r="J2">
-        <v>-4.798106449248422e-05</v>
+        <v>-1.74962138354967e-05</v>
       </c>
       <c r="K2">
-        <v>-3030.24</v>
+        <v>1401.6</v>
       </c>
       <c r="L2">
-        <v>-0.3303361967470458</v>
+        <v>0.1641256235509028</v>
       </c>
       <c r="M2">
-        <v>12.3101</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.001212925284015331</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.004062417498283964</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>12.3101</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.001212925284015331</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.004062417498283964</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>120285.7</v>
+        <v>115501.6</v>
       </c>
       <c r="V2">
-        <v>11.85185878550808</v>
+        <v>9.487407796816218</v>
       </c>
       <c r="W2">
-        <v>0.04149659863945578</v>
+        <v>0.04085226537265538</v>
       </c>
       <c r="X2">
-        <v>0.09964488699225962</v>
+        <v>0.1204772701431998</v>
       </c>
       <c r="Y2">
-        <v>-0.05814828835280384</v>
+        <v>-0.07962500477054441</v>
       </c>
       <c r="Z2">
-        <v>0.1750330903415173</v>
+        <v>0.6646430103073055</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03472859547190212</v>
+        <v>0.05784363232660819</v>
       </c>
       <c r="AC2">
-        <v>-0.03581726988659216</v>
+        <v>-0.05784363232660819</v>
       </c>
       <c r="AD2">
-        <v>98669.89999999999</v>
+        <v>37681.5</v>
       </c>
       <c r="AE2">
-        <v>8.875936810750616</v>
+        <v>6.402036378192479</v>
       </c>
       <c r="AF2">
-        <v>98678.77593681075</v>
+        <v>37687.9020363782</v>
       </c>
       <c r="AG2">
-        <v>-21606.92406318925</v>
+        <v>-77813.69796362179</v>
       </c>
       <c r="AH2">
-        <v>0.9067417248325887</v>
+        <v>0.7558426239006532</v>
       </c>
       <c r="AI2">
-        <v>0.7342095663009054</v>
+        <v>0.5485147639959058</v>
       </c>
       <c r="AJ2">
-        <v>1.885779005160866</v>
+        <v>1.185470644622344</v>
       </c>
       <c r="AK2">
-        <v>-1.530704173141498</v>
+        <v>1.662948871189347</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>81545.37190082645</v>
+        <v>35216.35514018691</v>
       </c>
       <c r="AP2">
-        <v>-17856.96203569359</v>
+        <v>-72723.08220899232</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ProCredit Holding AG &amp; Co. KGaA (XTRA:PCZ)</t>
+          <t>Merkur PrivatBank KgaA (XTRA:MBK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00413</v>
+        <v>0.229</v>
       </c>
       <c r="E3">
-        <v>0.116</v>
-      </c>
-      <c r="F3">
-        <v>0.38</v>
+        <v>0.251</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,97 +728,100 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-0.002203217545952836</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>-0.00111251579053064</v>
       </c>
       <c r="K3">
-        <v>81.2</v>
+        <v>10.2</v>
       </c>
       <c r="L3">
-        <v>0.2687851704733532</v>
+        <v>0.1068062827225131</v>
       </c>
       <c r="M3">
-        <v>12.3101</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.02301813762154076</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.1516022167487684</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>12.3101</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.02301813762154076</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.1516022167487684</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>138.3</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.2586013462976814</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>0.08805986335538445</v>
+        <v>0.04149715215622457</v>
       </c>
       <c r="X3">
-        <v>0.09964488699225962</v>
+        <v>0.1055832497911815</v>
       </c>
       <c r="Y3">
-        <v>-0.01158502363687518</v>
+        <v>-0.06408609763495694</v>
       </c>
       <c r="Z3">
-        <v>0.1143971523780673</v>
+        <v>1.940976573935622</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>-0.002159367087553441</v>
       </c>
       <c r="AB3">
-        <v>0.03413959225186732</v>
+        <v>0.05568416299049683</v>
       </c>
       <c r="AC3">
-        <v>-0.03413959225186732</v>
+        <v>-0.05784353007805027</v>
       </c>
       <c r="AD3">
-        <v>1968.4</v>
+        <v>243.6</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>6.402036378192479</v>
       </c>
       <c r="AF3">
-        <v>1968.4</v>
+        <v>250.0020363781925</v>
       </c>
       <c r="AG3">
-        <v>1830.1</v>
+        <v>250.0020363781925</v>
       </c>
       <c r="AH3">
-        <v>0.7863534675615214</v>
+        <v>0.6885173073438796</v>
       </c>
       <c r="AI3">
-        <v>0.664775413711584</v>
+        <v>0.512192160133676</v>
       </c>
       <c r="AJ3">
-        <v>0.7738593598037973</v>
+        <v>0.6885173073438796</v>
       </c>
       <c r="AK3">
-        <v>0.6483508697346512</v>
+        <v>0.512192160133676</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>227.6635514018691</v>
+      </c>
+      <c r="AP3">
+        <v>233.6467629702733</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Merkur PrivatBank KgaA (XTRA:MBK)</t>
+          <t>ProCredit Holding AG &amp; Co. KGaA (XTRA:PCZ)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,10 +841,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.173</v>
+        <v>-0.00638</v>
       </c>
       <c r="E4">
-        <v>0.237</v>
+        <v>-0.101</v>
+      </c>
+      <c r="F4">
+        <v>0.113</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,16 +856,16 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-0.006096951048005645</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>-0.003048475524002823</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>9.76</v>
+        <v>34.3</v>
       </c>
       <c r="L4">
-        <v>0.1052858683926645</v>
+        <v>0.1413267408323033</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -889,67 +889,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>476.6</v>
+        <v>132.9</v>
       </c>
       <c r="V4">
-        <v>3.680308880308881</v>
+        <v>0.5660136286201022</v>
       </c>
       <c r="W4">
-        <v>0.04149659863945578</v>
+        <v>0.03455571227080394</v>
       </c>
       <c r="X4">
-        <v>0.0748343252154109</v>
+        <v>0.1977719096125708</v>
       </c>
       <c r="Y4">
-        <v>-0.03333772657595512</v>
+        <v>-0.1632161973417668</v>
       </c>
       <c r="Z4">
-        <v>0.3571209301561143</v>
+        <v>0.08598150706770114</v>
       </c>
       <c r="AA4">
-        <v>-0.001088674414690036</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03472859547190212</v>
+        <v>0.05784363232660819</v>
       </c>
       <c r="AC4">
-        <v>-0.03581726988659216</v>
+        <v>-0.05784363232660819</v>
       </c>
       <c r="AD4">
-        <v>273.6</v>
+        <v>1698.5</v>
       </c>
       <c r="AE4">
-        <v>8.875936810750616</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>282.4759368107506</v>
+        <v>1698.5</v>
       </c>
       <c r="AG4">
-        <v>-194.1240631892494</v>
+        <v>1565.6</v>
       </c>
       <c r="AH4">
-        <v>0.685661252444731</v>
+        <v>0.8785496301660374</v>
       </c>
       <c r="AI4">
-        <v>0.5347128595636653</v>
+        <v>0.6614611729885504</v>
       </c>
       <c r="AJ4">
-        <v>3.003897520661361</v>
+        <v>0.8695845367696068</v>
       </c>
       <c r="AK4">
-        <v>-3.756565921585073</v>
+        <v>0.6429832847344861</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>226.1157024793389</v>
-      </c>
-      <c r="AP4">
-        <v>-160.4331100737598</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0279</v>
+        <v>-0.00624</v>
+      </c>
+      <c r="E5">
+        <v>0.424</v>
+      </c>
+      <c r="F5">
+        <v>0.556</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,10 +984,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>-3121.2</v>
+        <v>1357.1</v>
       </c>
       <c r="L5">
-        <v>-0.355554542969106</v>
+        <v>0.1654677136168552</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -996,7 +996,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1005,61 +1005,61 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>119670.8</v>
+        <v>115368.7</v>
       </c>
       <c r="V5">
-        <v>12.6171136977058</v>
+        <v>9.75526580587335</v>
       </c>
       <c r="W5">
-        <v>-0.08644235376225859</v>
+        <v>0.04085226537265538</v>
       </c>
       <c r="X5">
-        <v>0.206971551213983</v>
+        <v>0.1204772701431998</v>
       </c>
       <c r="Y5">
-        <v>-0.2934139049762416</v>
+        <v>-0.07962500477054441</v>
       </c>
       <c r="Z5">
-        <v>0.1773127575341359</v>
+        <v>0.8220671958944762</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03708072867516726</v>
+        <v>0.05988139861064851</v>
       </c>
       <c r="AC5">
-        <v>-0.03708072867516726</v>
+        <v>-0.05988139861064851</v>
       </c>
       <c r="AD5">
-        <v>96427.89999999999</v>
+        <v>35739.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>96427.89999999999</v>
+        <v>35739.4</v>
       </c>
       <c r="AG5">
-        <v>-23242.90000000001</v>
+        <v>-79629.29999999999</v>
       </c>
       <c r="AH5">
-        <v>0.9104470002181041</v>
+        <v>0.7513691588686806</v>
       </c>
       <c r="AI5">
-        <v>0.736585082662336</v>
+        <v>0.5443672880640823</v>
       </c>
       <c r="AJ5">
-        <v>1.689397518552707</v>
+        <v>1.174421485774966</v>
       </c>
       <c r="AK5">
-        <v>-2.067634526255863</v>
+        <v>1.601696449404211</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/research/traditional_assets/database/data/germany/germany_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00624</v>
+        <v>0.15905</v>
       </c>
       <c r="E2">
-        <v>0.251</v>
+        <v>0.1785</v>
       </c>
       <c r="F2">
-        <v>0.3345</v>
+        <v>0.9940000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,16 +603,16 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-2.463843130266467e-05</v>
+        <v>-0.0005680245348119269</v>
       </c>
       <c r="J2">
-        <v>-1.74962138354967e-05</v>
+        <v>-0.0003713559254001807</v>
       </c>
       <c r="K2">
-        <v>1401.6</v>
+        <v>109.7</v>
       </c>
       <c r="L2">
-        <v>0.1641256235509028</v>
+        <v>0.2229221702905913</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>115501.6</v>
+        <v>216.8</v>
       </c>
       <c r="V2">
-        <v>9.487407796816218</v>
+        <v>0.3248426730596344</v>
       </c>
       <c r="W2">
-        <v>0.04085226537265538</v>
+        <v>0.08002183105998527</v>
       </c>
       <c r="X2">
-        <v>0.1204772701431998</v>
+        <v>0.08804815833898201</v>
       </c>
       <c r="Y2">
-        <v>-0.07962500477054441</v>
+        <v>-0.008026327278996742</v>
       </c>
       <c r="Z2">
-        <v>0.6646430103073055</v>
+        <v>0.1684098780577649</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>-0.0001434527223921846</v>
       </c>
       <c r="AB2">
-        <v>0.05784363232660819</v>
+        <v>0.04950381285715064</v>
       </c>
       <c r="AC2">
-        <v>-0.05784363232660819</v>
+        <v>-0.04964726557954283</v>
       </c>
       <c r="AD2">
-        <v>37681.5</v>
+        <v>1848.9</v>
       </c>
       <c r="AE2">
-        <v>6.402036378192479</v>
+        <v>5.437624367904746</v>
       </c>
       <c r="AF2">
-        <v>37687.9020363782</v>
+        <v>1854.337624367905</v>
       </c>
       <c r="AG2">
-        <v>-77813.69796362179</v>
+        <v>1637.537624367905</v>
       </c>
       <c r="AH2">
-        <v>0.7558426239006532</v>
+        <v>0.7353412212472781</v>
       </c>
       <c r="AI2">
-        <v>0.5485147639959058</v>
+        <v>0.5825685534383664</v>
       </c>
       <c r="AJ2">
-        <v>1.185470644622344</v>
+        <v>0.7104476958750566</v>
       </c>
       <c r="AK2">
-        <v>1.662948871189347</v>
+        <v>0.5520588138035161</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>35216.35514018691</v>
+        <v>2288.242574257426</v>
       </c>
       <c r="AP2">
-        <v>-72723.08220899232</v>
+        <v>2026.655475702852</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.229</v>
+        <v>0.232</v>
       </c>
       <c r="E3">
-        <v>0.251</v>
+        <v>0.231</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,16 +728,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-0.002203217545952836</v>
+        <v>-0.002602652454198782</v>
       </c>
       <c r="J3">
-        <v>-0.00111251579053064</v>
+        <v>-0.001301326227099391</v>
       </c>
       <c r="K3">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="L3">
-        <v>0.1068062827225131</v>
+        <v>0.1033519553072626</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>32.1</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.2291220556745182</v>
       </c>
       <c r="W3">
-        <v>0.04149715215622457</v>
+        <v>0.04661906761864763</v>
       </c>
       <c r="X3">
-        <v>0.1055832497911815</v>
+        <v>0.08102163269765636</v>
       </c>
       <c r="Y3">
-        <v>-0.06408609763495694</v>
+        <v>-0.03440256507900873</v>
       </c>
       <c r="Z3">
-        <v>1.940976573935622</v>
+        <v>0.2204715764653963</v>
       </c>
       <c r="AA3">
-        <v>-0.002159367087553441</v>
+        <v>-0.0002869054447843691</v>
       </c>
       <c r="AB3">
-        <v>0.05568416299049683</v>
+        <v>0.04858155642073775</v>
       </c>
       <c r="AC3">
-        <v>-0.05784353007805027</v>
+        <v>-0.04886846186552211</v>
       </c>
       <c r="AD3">
-        <v>243.6</v>
+        <v>261.1</v>
       </c>
       <c r="AE3">
-        <v>6.402036378192479</v>
+        <v>5.437624367904746</v>
       </c>
       <c r="AF3">
-        <v>250.0020363781925</v>
+        <v>266.5376243679048</v>
       </c>
       <c r="AG3">
-        <v>250.0020363781925</v>
+        <v>234.4376243679048</v>
       </c>
       <c r="AH3">
-        <v>0.6885173073438796</v>
+        <v>0.6554671983002617</v>
       </c>
       <c r="AI3">
-        <v>0.512192160133676</v>
+        <v>0.4727205366380244</v>
       </c>
       <c r="AJ3">
-        <v>0.6885173073438796</v>
+        <v>0.6259387818875545</v>
       </c>
       <c r="AK3">
-        <v>0.512192160133676</v>
+        <v>0.4408896674306036</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -818,10 +818,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>227.6635514018691</v>
+        <v>323.1435643564357</v>
       </c>
       <c r="AP3">
-        <v>233.6467629702733</v>
+        <v>290.1455747127534</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ProCredit Holding AG &amp; Co. KGaA (XTRA:PCZ)</t>
+          <t>ProCredit Holding AG (XTRA:PCZ)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.00638</v>
+        <v>0.0861</v>
       </c>
       <c r="E4">
-        <v>-0.101</v>
+        <v>0.126</v>
       </c>
       <c r="F4">
-        <v>0.113</v>
+        <v>0.9940000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>34.3</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="L4">
-        <v>0.1413267408323033</v>
+        <v>0.2563036132050949</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -889,182 +889,60 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>132.9</v>
+        <v>184.7</v>
       </c>
       <c r="V4">
-        <v>0.5660136286201022</v>
+        <v>0.3502749857765978</v>
       </c>
       <c r="W4">
-        <v>0.03455571227080394</v>
+        <v>0.1134245945013229</v>
       </c>
       <c r="X4">
-        <v>0.1977719096125708</v>
+        <v>0.09507468398030766</v>
       </c>
       <c r="Y4">
-        <v>-0.1632161973417668</v>
+        <v>0.01834991052101524</v>
       </c>
       <c r="Z4">
-        <v>0.08598150706770114</v>
+        <v>0.1579941681383219</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05784363232660819</v>
+        <v>0.05042606929356353</v>
       </c>
       <c r="AC4">
-        <v>-0.05784363232660819</v>
+        <v>-0.05042606929356353</v>
       </c>
       <c r="AD4">
-        <v>1698.5</v>
+        <v>1587.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1698.5</v>
+        <v>1587.8</v>
       </c>
       <c r="AG4">
-        <v>1565.6</v>
+        <v>1403.1</v>
       </c>
       <c r="AH4">
-        <v>0.8785496301660374</v>
+        <v>0.7506973665547728</v>
       </c>
       <c r="AI4">
-        <v>0.6614611729885504</v>
+        <v>0.606215638362859</v>
       </c>
       <c r="AJ4">
-        <v>0.8695845367696068</v>
+        <v>0.7268441773725652</v>
       </c>
       <c r="AK4">
-        <v>0.6429832847344861</v>
+        <v>0.5763401109057301</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Commerzbank AG (XTRA:CBK)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>-0.00624</v>
-      </c>
-      <c r="E5">
-        <v>0.424</v>
-      </c>
-      <c r="F5">
-        <v>0.556</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>1357.1</v>
-      </c>
-      <c r="L5">
-        <v>0.1654677136168552</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>-0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>-0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>115368.7</v>
-      </c>
-      <c r="V5">
-        <v>9.75526580587335</v>
-      </c>
-      <c r="W5">
-        <v>0.04085226537265538</v>
-      </c>
-      <c r="X5">
-        <v>0.1204772701431998</v>
-      </c>
-      <c r="Y5">
-        <v>-0.07962500477054441</v>
-      </c>
-      <c r="Z5">
-        <v>0.8220671958944762</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.05988139861064851</v>
-      </c>
-      <c r="AC5">
-        <v>-0.05988139861064851</v>
-      </c>
-      <c r="AD5">
-        <v>35739.4</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>35739.4</v>
-      </c>
-      <c r="AG5">
-        <v>-79629.29999999999</v>
-      </c>
-      <c r="AH5">
-        <v>0.7513691588686806</v>
-      </c>
-      <c r="AI5">
-        <v>0.5443672880640823</v>
-      </c>
-      <c r="AJ5">
-        <v>1.174421485774966</v>
-      </c>
-      <c r="AK5">
-        <v>1.601696449404211</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
         <v>0</v>
       </c>
     </row>
